--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209812</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209826</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209829</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209843</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209845</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209865</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209866</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209854</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209810</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209823</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209827</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209844</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209852</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209819</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209868</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209820</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209821</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209822</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,6 +3009,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209828</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3000,6 +3115,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209842</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3101,6 +3221,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209847</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3202,6 +3327,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209848</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3303,6 +3433,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209871</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3404,6 +3539,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209824</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3505,6 +3645,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209863</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3606,6 +3751,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209832</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3707,6 +3857,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209833</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3808,6 +3963,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209838</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3909,6 +4069,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209840</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4010,6 +4175,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209857</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4111,6 +4281,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209849</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209825</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4313,6 +4493,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209813</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4414,6 +4599,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209831</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4515,6 +4705,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209846</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4616,6 +4811,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209867</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4717,6 +4917,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209851</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4818,6 +5023,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209864</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4929,6 +5139,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209811</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5040,6 +5255,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209815</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5151,6 +5371,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209816</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5262,6 +5487,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209817</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5373,6 +5603,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209818</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5479,6 +5714,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209850</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5589,6 +5829,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209835</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5699,6 +5944,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209837</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5800,6 +6050,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209853</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5910,6 +6165,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209856</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6020,6 +6280,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209858</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6130,6 +6395,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209861</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6240,6 +6510,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209862</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6341,6 +6616,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209836</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6442,6 +6722,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209860</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6543,6 +6828,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209870</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6644,6 +6934,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209830</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6745,6 +7040,11 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209841</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6846,8 +7146,75 @@
           <t>Stenvalls trä AB - Second opinion 2026</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135209869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135209859</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135209812</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135209826</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135209829</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135209843</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135209845</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135209865</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>135209866</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135209839</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>135209854</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135209810</v>
       </c>
       <c r="B12" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>135209823</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135209827</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135209844</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>135209852</v>
       </c>
       <c r="B16" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135209819</v>
       </c>
       <c r="B17" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>135209868</v>
       </c>
       <c r="B18" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135209814</v>
       </c>
       <c r="B19" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135209820</v>
       </c>
       <c r="B20" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135209821</v>
       </c>
       <c r="B21" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>135209822</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135209828</v>
       </c>
       <c r="B23" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135209842</v>
       </c>
       <c r="B24" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>135209847</v>
       </c>
       <c r="B25" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135209848</v>
       </c>
       <c r="B26" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>135209871</v>
       </c>
       <c r="B27" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135209824</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>135209863</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135209832</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135209833</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>135209838</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>135209840</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135209857</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>135209849</v>
       </c>
       <c r="B35" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>135209825</v>
       </c>
       <c r="B36" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135209813</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>135209831</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>135209846</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>135209867</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135209851</v>
       </c>
       <c r="B41" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>135209864</v>
       </c>
       <c r="B42" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>135209811</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>135209815</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135209816</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>135209817</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>135209818</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135209850</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135209835</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135209837</v>
       </c>
       <c r="B50" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135209853</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135209856</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135209858</v>
       </c>
       <c r="B53" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>135209861</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135209862</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>135209836</v>
       </c>
       <c r="B56" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>135209860</v>
       </c>
       <c r="B57" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135209870</v>
       </c>
       <c r="B58" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>135209830</v>
       </c>
       <c r="B59" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135209841</v>
       </c>
       <c r="B60" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135209869</v>
       </c>
       <c r="B61" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135209859</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135209812</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135209826</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135209829</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135209843</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135209845</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135209865</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>135209866</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135209839</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>135209854</v>
       </c>
       <c r="B11" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135209810</v>
       </c>
       <c r="B12" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>135209823</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135209827</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135209844</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>135209852</v>
       </c>
       <c r="B16" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135209819</v>
       </c>
       <c r="B17" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>135209868</v>
       </c>
       <c r="B18" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135209814</v>
       </c>
       <c r="B19" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135209820</v>
       </c>
       <c r="B20" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135209821</v>
       </c>
       <c r="B21" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>135209822</v>
       </c>
       <c r="B22" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135209828</v>
       </c>
       <c r="B23" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135209842</v>
       </c>
       <c r="B24" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>135209847</v>
       </c>
       <c r="B25" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135209848</v>
       </c>
       <c r="B26" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>135209871</v>
       </c>
       <c r="B27" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135209824</v>
       </c>
       <c r="B28" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>135209863</v>
       </c>
       <c r="B29" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135209832</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>135209833</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>135209838</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>135209840</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>135209857</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>135209849</v>
       </c>
       <c r="B35" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>135209825</v>
       </c>
       <c r="B36" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135209813</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>135209831</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>135209846</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>135209867</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>135209851</v>
       </c>
       <c r="B41" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>135209864</v>
       </c>
       <c r="B42" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135209835</v>
       </c>
       <c r="B49" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135209837</v>
       </c>
       <c r="B50" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135209853</v>
       </c>
       <c r="B51" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135209856</v>
       </c>
       <c r="B52" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135209858</v>
       </c>
       <c r="B53" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>135209861</v>
       </c>
       <c r="B54" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135209862</v>
       </c>
       <c r="B55" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>135209836</v>
       </c>
       <c r="B56" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>135209860</v>
       </c>
       <c r="B57" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135209870</v>
       </c>
       <c r="B58" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>135209830</v>
       </c>
       <c r="B59" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135209841</v>
       </c>
       <c r="B60" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>135209869</v>
       </c>
       <c r="B61" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 22414-2026 artfynd.xlsx
+++ b/artfynd/A 22414-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135209859</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>135209839</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135209810</v>
       </c>
       <c r="B12" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>135209823</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>135209827</v>
       </c>
       <c r="B14" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135209844</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>135209852</v>
       </c>
       <c r="B16" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>135209819</v>
       </c>
       <c r="B17" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>135209868</v>
       </c>
       <c r="B18" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>135209814</v>
       </c>
       <c r="B19" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>135209820</v>
       </c>
       <c r="B20" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>135209821</v>
       </c>
       <c r="B21" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>135209822</v>
       </c>
       <c r="B22" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135209828</v>
       </c>
       <c r="B23" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135209842</v>
       </c>
       <c r="B24" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>135209847</v>
       </c>
       <c r="B25" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135209848</v>
       </c>
       <c r="B26" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>135209871</v>
       </c>
       <c r="B27" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135209824</v>
       </c>
       <c r="B28" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>135209863</v>
       </c>
       <c r="B29" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135209835</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135209837</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>135209853</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135209856</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135209858</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>135209861</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>135209862</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>135209836</v>
       </c>
       <c r="B56" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>135209860</v>
       </c>
       <c r="B57" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
